--- a/Use-Case_Description--Share_Annotated_Audio_Files.xlsx
+++ b/Use-Case_Description--Share_Annotated_Audio_Files.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{902A6C99-A204-453B-930A-40E82C24C4C1}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{080209AB-C56C-4066-8BF7-1758AD26B066}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="130" yWindow="50" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
+    <workbookView xWindow="19170" yWindow="80" windowWidth="19060" windowHeight="20670" xr2:uid="{F029340B-59BC-4187-9937-02EC323D7EB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -206,12 +206,14 @@
 2. The system provides the set of annotated audio files that the Sharer has permission to share.
 3. The Sharer designates the annotated audio file(s) to share.
 4. The Sharer specifies the Receiver(s) with whom the annotated audio file(s) will be shared.
-5. The system shares the annotated audio file(s) with the specified Receiver(s).</t>
+5. The Sharer requests that the system share the annotated audio file(s) with the specified Receiver(s).
+6. The system shares the annotated audio file(s) with the specified Receiver(s).</t>
   </si>
   <si>
     <t>Sharer: (1) Signal of desire to share annotated audio files
 Sharer: (3) Designation of annotated audio file(s) to share
-Sharer: (4) Specification of Receiver(s) with whom the annotated audio file(s) will be shared</t>
+Sharer: (4) Specification of Receiver(s) with whom the annotated audio file(s) will be shared
+Sharer: (5) Request that the system share the annotated audio file(s) with the specified Receiver(s)</t>
   </si>
 </sst>
 </file>
@@ -781,7 +783,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" ht="87" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>25</v>
       </c>
@@ -822,7 +824,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" ht="58" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>13</v>
       </c>
